--- a/artfynd/A 44969-2021 artfynd.xlsx
+++ b/artfynd/A 44969-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 44969-2021 artfynd.xlsx
+++ b/artfynd/A 44969-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AY40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>67811787</v>
+        <v>67811468</v>
       </c>
       <c r="B2" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93186</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4366</v>
+        <v>150</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Pers.) Fayod</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gruvebo (400 m sydsydväst om ), Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533739.0012159211</v>
+        <v>533757</v>
       </c>
       <c r="R2" t="n">
-        <v>6334028.579612884</v>
+        <v>6334046</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +752,9 @@
           <t>2017-09-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-09-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,15 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>67811922</v>
+        <v>96354007</v>
       </c>
       <c r="B3" t="n">
-        <v>44175</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87237</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,51 +797,45 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102421</v>
+        <v>1980</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Slåttergubbemal</t>
+          <t>Porslinsblå spindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Digitivalva arnicella</t>
+          <t>Cortinarius cumatilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(von Heyden, 1863)</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>mina</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gruvebo (400 m sydsydväst om ), Sm</t>
+          <t>Kalkbarrskog S. om Gruvebo, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533659.9674060588</v>
+        <v>533743</v>
       </c>
       <c r="R3" t="n">
-        <v>6334188.506679389</v>
+        <v>6334185</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,22 +862,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-09-11</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-09-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,13 +876,9 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Kalkgranskog.</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -922,54 +891,64 @@
           <t>Tobias Ivarsson</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020, Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>67811321</v>
+        <v>96353825</v>
       </c>
       <c r="B4" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87322</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5964</v>
+        <v>1988</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gruvebo (400 m sydsydväst om ), Sm</t>
+          <t>Kalkbarrskog S. om Gruvebo, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>533629.5046719594</v>
+        <v>533640</v>
       </c>
       <c r="R4" t="n">
-        <v>6334191.513078528</v>
+        <v>6334175</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,22 +975,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2017-09-11</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2017-09-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,11 +993,6 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Kalkgranskog.</t>
-        </is>
-      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
@@ -1040,63 +1004,64 @@
           <t>Tobias Ivarsson</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020, Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>67811468</v>
+        <v>96354062</v>
       </c>
       <c r="B5" t="n">
-        <v>90642</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87322</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>150</v>
+        <v>1988</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gruvebo (400 m sydsydväst om ), Sm</t>
+          <t>Kalkbarrskog S. om Gruvebo, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>533757.3434960862</v>
+        <v>533785</v>
       </c>
       <c r="R5" t="n">
-        <v>6334045.546632628</v>
+        <v>6334152</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1123,22 +1088,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2017-09-11</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2017-09-11</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,13 +1102,9 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Kalkgranskog.</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1166,54 +1117,64 @@
           <t>Tobias Ivarsson</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020, Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>67811327</v>
+        <v>96354078</v>
       </c>
       <c r="B6" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87322</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5964</v>
+        <v>1988</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gruvebo (400 m sydsydväst om ), Sm</t>
+          <t>Kalkbarrskog S. om Gruvebo, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>533739.0012159211</v>
+        <v>533753</v>
       </c>
       <c r="R6" t="n">
-        <v>6334028.579612884</v>
+        <v>6334179</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1240,22 +1201,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2017-09-11</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2017-09-11</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1268,11 +1219,6 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Kalkgranskog.</t>
-        </is>
-      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
@@ -1284,41 +1230,40 @@
           <t>Tobias Ivarsson</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020, Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>67811326</v>
+        <v>67811783</v>
       </c>
       <c r="B7" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5964</v>
+        <v>4366</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1328,10 +1273,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>533757.3434960862</v>
+        <v>533660</v>
       </c>
       <c r="R7" t="n">
-        <v>6334045.546632628</v>
+        <v>6334189</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1361,28 +1306,17 @@
           <t>2017-09-11</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2017-09-11</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1406,37 +1340,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>67811582</v>
+        <v>67811785</v>
       </c>
       <c r="B8" t="n">
-        <v>88921</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5741</v>
+        <v>4366</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1446,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>533629.5046719594</v>
+        <v>533726</v>
       </c>
       <c r="R8" t="n">
-        <v>6334191.513078528</v>
+        <v>6333999</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1479,19 +1408,9 @@
           <t>2017-09-11</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2017-09-11</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1523,19 +1442,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>67811783</v>
+        <v>67811786</v>
       </c>
       <c r="B9" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1563,10 +1477,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>533659.9674060588</v>
+        <v>533757</v>
       </c>
       <c r="R9" t="n">
-        <v>6334188.506679389</v>
+        <v>6334046</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1596,19 +1510,9 @@
           <t>2017-09-11</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2017-09-11</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1640,61 +1544,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>67811920</v>
+        <v>67811787</v>
       </c>
       <c r="B10" t="n">
-        <v>104838</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219955</v>
+        <v>4366</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Arnica montana</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gruvebo (400 m sydsydväst om ), Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>533739.0012159211</v>
+        <v>533739</v>
       </c>
       <c r="R10" t="n">
-        <v>6334028.579612884</v>
+        <v>6334029</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1724,19 +1612,9 @@
           <t>2017-09-11</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2017-09-11</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1768,37 +1646,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>67811325</v>
+        <v>67811581</v>
       </c>
       <c r="B11" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91409</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5964</v>
+        <v>5741</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1808,10 +1681,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>533725.6569288654</v>
+        <v>533660</v>
       </c>
       <c r="R11" t="n">
-        <v>6333998.63373314</v>
+        <v>6334189</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1841,28 +1714,17 @@
           <t>2017-09-11</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2017-09-11</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1886,37 +1748,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>67811785</v>
+        <v>67811582</v>
       </c>
       <c r="B12" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91409</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4366</v>
+        <v>5741</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1926,10 +1783,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>533725.6569288654</v>
+        <v>533630</v>
       </c>
       <c r="R12" t="n">
-        <v>6333998.63373314</v>
+        <v>6334192</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1959,19 +1816,9 @@
           <t>2017-09-11</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2017-09-11</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2003,50 +1850,56 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>67811786</v>
+        <v>96353809</v>
       </c>
       <c r="B13" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91409</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4366</v>
+        <v>5741</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gruvebo (400 m sydsydväst om ), Sm</t>
+          <t>Kalkbarrskog S. om Gruvebo, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>533757.3434960862</v>
+        <v>533638</v>
       </c>
       <c r="R13" t="n">
-        <v>6334045.546632628</v>
+        <v>6334175</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2073,22 +1926,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2017-09-11</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2017-09-11</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2097,13 +1940,9 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Kalkgranskog.</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2116,65 +1955,64 @@
           <t>Tobias Ivarsson</t>
         </is>
       </c>
-      <c r="AY13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020, Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>67811919</v>
+        <v>96353847</v>
       </c>
       <c r="B14" t="n">
-        <v>104838</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91409</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219955</v>
+        <v>5741</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Arnica montana</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gruvebo (400 m sydsydväst om ), Sm</t>
+          <t>Kalkbarrskog S. om Gruvebo, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>533659.9674060588</v>
+        <v>533662</v>
       </c>
       <c r="R14" t="n">
-        <v>6334188.506679389</v>
+        <v>6334157</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2201,22 +2039,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2017-09-11</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2017-09-11</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2225,13 +2053,9 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Kalkgranskog.</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2244,41 +2068,40 @@
           <t>Tobias Ivarsson</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020, Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>67811581</v>
+        <v>67811320</v>
       </c>
       <c r="B15" t="n">
-        <v>88921</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5741</v>
+        <v>5964</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2288,10 +2111,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>533659.9674060588</v>
+        <v>533660</v>
       </c>
       <c r="R15" t="n">
-        <v>6334188.506679389</v>
+        <v>6334189</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2321,27 +2144,18 @@
           <t>2017-09-11</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2017-09-11</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2365,19 +2179,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>67811320</v>
+        <v>67811321</v>
       </c>
       <c r="B16" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2390,12 +2199,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2405,10 +2214,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>533659.9674060588</v>
+        <v>533630</v>
       </c>
       <c r="R16" t="n">
-        <v>6334188.506679389</v>
+        <v>6334192</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2438,19 +2247,9 @@
           <t>2017-09-11</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2017-09-11</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2483,37 +2282,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>67811219</v>
+        <v>67811322</v>
       </c>
       <c r="B17" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2523,10 +2317,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>533757.3434960862</v>
+        <v>533673</v>
       </c>
       <c r="R17" t="n">
-        <v>6334045.546632628</v>
+        <v>6334030</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2556,27 +2350,18 @@
           <t>2017-09-11</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2017-09-11</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2600,61 +2385,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>96354078</v>
+        <v>67811324</v>
       </c>
       <c r="B18" t="n">
-        <v>85253</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1988</v>
+        <v>5964</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kalkbarrskog S. om Gruvebo, Sm</t>
+          <t>Gruvebo (400 m sydsydväst om ), Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>533752.9908420054</v>
+        <v>533680</v>
       </c>
       <c r="R18" t="n">
-        <v>6334178.959722904</v>
+        <v>6334022</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2681,22 +2450,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-09-11</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-09-11</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2709,6 +2468,11 @@
       <c r="AG18" t="b">
         <v>0</v>
       </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
+        </is>
+      </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
@@ -2720,27 +2484,18 @@
           <t>Tobias Ivarsson</t>
         </is>
       </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020, Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
-        </is>
-      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>96353736</v>
+        <v>67811325</v>
       </c>
       <c r="B19" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2753,36 +2508,25 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kalkbarrskog S. om Gruvebo, Sm</t>
+          <t>Gruvebo (400 m sydsydväst om ), Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>533628.5726184119</v>
+        <v>533726</v>
       </c>
       <c r="R19" t="n">
-        <v>6334105.795335921</v>
+        <v>6333999</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2809,22 +2553,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-09-11</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-09-11</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2837,6 +2571,11 @@
       <c r="AG19" t="b">
         <v>0</v>
       </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
+        </is>
+      </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
@@ -2848,27 +2587,18 @@
           <t>Tobias Ivarsson</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020, Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
-        </is>
-      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>96354311</v>
+        <v>67811326</v>
       </c>
       <c r="B20" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2881,36 +2611,25 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kalkbarrskog S. om Gruvebo, Sm</t>
+          <t>Gruvebo (400 m sydsydväst om ), Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>533726.297992997</v>
+        <v>533757</v>
       </c>
       <c r="R20" t="n">
-        <v>6333986.704193462</v>
+        <v>6334046</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2937,22 +2656,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-09-11</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-09-11</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2965,6 +2674,11 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
+        </is>
+      </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
@@ -2976,67 +2690,49 @@
           <t>Tobias Ivarsson</t>
         </is>
       </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020, Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
-        </is>
-      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>96354327</v>
+        <v>67811327</v>
       </c>
       <c r="B21" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100526</v>
+        <v>5964</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kalkbarrskog S. om Gruvebo, Sm</t>
+          <t>Gruvebo (400 m sydsydväst om ), Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>533729.5928056925</v>
+        <v>533739</v>
       </c>
       <c r="R21" t="n">
-        <v>6334049.117088572</v>
+        <v>6334029</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3063,22 +2759,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-09-11</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-09-11</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3091,6 +2777,11 @@
       <c r="AG21" t="b">
         <v>0</v>
       </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
+        </is>
+      </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
@@ -3102,27 +2793,18 @@
           <t>Tobias Ivarsson</t>
         </is>
       </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020, Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
-        </is>
-      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>96353769</v>
+        <v>96353736</v>
       </c>
       <c r="B22" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -3135,12 +2817,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3161,10 +2843,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>533623.2388353636</v>
+        <v>533629</v>
       </c>
       <c r="R22" t="n">
-        <v>6334226.722004616</v>
+        <v>6334106</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3194,19 +2876,9 @@
           <t>2021-09-27</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2021-09-27</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3238,19 +2910,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>96354299</v>
+        <v>96353758</v>
       </c>
       <c r="B23" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -3263,12 +2930,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3289,10 +2956,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>533759.493283121</v>
+        <v>533630</v>
       </c>
       <c r="R23" t="n">
-        <v>6333982.093208997</v>
+        <v>6334150</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3322,19 +2989,9 @@
           <t>2021-09-27</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2021-09-27</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3366,19 +3023,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>96354335</v>
+        <v>96353769</v>
       </c>
       <c r="B24" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3391,12 +3043,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3417,10 +3069,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>533705.7531548589</v>
+        <v>533623</v>
       </c>
       <c r="R24" t="n">
-        <v>6334039.700081617</v>
+        <v>6334226</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3450,19 +3102,9 @@
           <t>2021-09-27</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2021-09-27</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3494,47 +3136,42 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>96353809</v>
+        <v>96353788</v>
       </c>
       <c r="B25" t="n">
-        <v>88921</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5741</v>
+        <v>5964</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -3545,10 +3182,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>533637.7942998203</v>
+        <v>533642</v>
       </c>
       <c r="R25" t="n">
-        <v>6334174.76423916</v>
+        <v>6334188</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3578,19 +3215,9 @@
           <t>2021-09-27</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2021-09-27</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3622,19 +3249,14 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>96353788</v>
+        <v>96354067</v>
       </c>
       <c r="B26" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3647,12 +3269,12 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3673,10 +3295,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>533642.0362052908</v>
+        <v>533785</v>
       </c>
       <c r="R26" t="n">
-        <v>6334187.817982269</v>
+        <v>6334152</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3706,19 +3328,9 @@
           <t>2021-09-27</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2021-09-27</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3750,47 +3362,42 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>96354007</v>
+        <v>96354179</v>
       </c>
       <c r="B27" t="n">
-        <v>85176</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1980</v>
+        <v>5964</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Porslinsblå spindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius cumatilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -3801,10 +3408,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>533742.6154540972</v>
+        <v>533788</v>
       </c>
       <c r="R27" t="n">
-        <v>6334184.841983688</v>
+        <v>6334192</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3834,19 +3441,9 @@
           <t>2021-09-27</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2021-09-27</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3878,37 +3475,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>96353825</v>
+        <v>96354299</v>
       </c>
       <c r="B28" t="n">
-        <v>85253</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1988</v>
+        <v>5964</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3918,7 +3510,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -3929,10 +3521,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>533639.9683219307</v>
+        <v>533759</v>
       </c>
       <c r="R28" t="n">
-        <v>6334174.78196233</v>
+        <v>6333982</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3962,19 +3554,9 @@
           <t>2021-09-27</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2021-09-27</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4006,47 +3588,42 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>96353847</v>
+        <v>96354311</v>
       </c>
       <c r="B29" t="n">
-        <v>88921</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5741</v>
+        <v>5964</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -4057,10 +3634,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>533662.398076578</v>
+        <v>533726</v>
       </c>
       <c r="R29" t="n">
-        <v>6334157.063467992</v>
+        <v>6333987</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4090,19 +3667,9 @@
           <t>2021-09-27</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2021-09-27</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4134,19 +3701,14 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>96353758</v>
+        <v>96354335</v>
       </c>
       <c r="B30" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -4159,12 +3721,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -4185,10 +3747,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>533630.3797414304</v>
+        <v>533705</v>
       </c>
       <c r="R30" t="n">
-        <v>6334150.835235199</v>
+        <v>6334040</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4218,19 +3780,9 @@
           <t>2021-09-27</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2021-09-27</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4262,15 +3814,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>96354330</v>
+        <v>67811189</v>
       </c>
       <c r="B31" t="n">
-        <v>4711</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4278,43 +3825,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100299</v>
+        <v>6031</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kalkbarrskog S. om Gruvebo, Sm</t>
+          <t>Gruvebo (400 m sydsydväst om ), Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>533729.5928056925</v>
+        <v>533766</v>
       </c>
       <c r="R31" t="n">
-        <v>6334049.117088572</v>
+        <v>6334204</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4341,22 +3879,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-09-11</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-09-11</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4369,6 +3897,11 @@
       <c r="AG31" t="b">
         <v>0</v>
       </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
+        </is>
+      </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
@@ -4380,11 +3913,994 @@
           <t>Tobias Ivarsson</t>
         </is>
       </c>
-      <c r="AY31" t="inlineStr">
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>96354330</v>
+      </c>
+      <c r="B32" t="n">
+        <v>4775</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog S. om Gruvebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>533730</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6334049</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Fagerhult</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
         <is>
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020, Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
         </is>
       </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>96354327</v>
+      </c>
+      <c r="B33" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog S. om Gruvebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>533730</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6334049</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Fagerhult</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020, Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>67811922</v>
+      </c>
+      <c r="B34" t="n">
+        <v>44889</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>102421</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Slåttergubbemal</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Digitivalva arnicella</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(von Heyden, 1863)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>mina</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Gruvebo (400 m sydsydväst om ), Sm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>533660</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6334189</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Fagerhult</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2017-09-11</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2017-09-11</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>67811919</v>
+      </c>
+      <c r="B35" t="n">
+        <v>107908</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>219955</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Slåttergubbe</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Arnica montana</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Gruvebo (400 m sydsydväst om ), Sm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>533660</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6334189</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Fagerhult</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2017-09-11</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2017-09-11</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>67811920</v>
+      </c>
+      <c r="B36" t="n">
+        <v>107908</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>219955</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Slåttergubbe</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Arnica montana</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Gruvebo (400 m sydsydväst om ), Sm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>533739</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6334029</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Fagerhult</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2017-09-11</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2017-09-11</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>96353724</v>
+      </c>
+      <c r="B37" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog S. om Gruvebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>533630</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6334086</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Fagerhult</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020, Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>67811215</v>
+      </c>
+      <c r="B38" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Gruvebo (400 m sydsydväst om ), Sm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>533673</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6334030</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Fagerhult</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2017-09-11</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2017-09-11</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>67811218</v>
+      </c>
+      <c r="B39" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Gruvebo (400 m sydsydväst om ), Sm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>533680</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6334022</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Fagerhult</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2017-09-11</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2017-09-11</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>67811219</v>
+      </c>
+      <c r="B40" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Gruvebo (400 m sydsydväst om ), Sm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>533757</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6334046</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Fagerhult</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2017-09-11</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2017-09-11</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44969-2021 artfynd.xlsx
+++ b/artfynd/A 44969-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AZ40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67811468</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020, Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96354007</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1009,6 +1024,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020, Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96353825</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1122,6 +1142,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020, Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96354062</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1235,6 +1260,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020, Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96354078</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1337,6 +1367,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67811783</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1439,6 +1474,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67811785</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1541,6 +1581,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67811786</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1643,6 +1688,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67811787</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1745,6 +1795,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67811581</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1847,6 +1902,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67811582</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1960,6 +2020,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020, Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96353809</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2073,6 +2138,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020, Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96353847</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2176,6 +2246,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67811320</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2279,6 +2354,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67811321</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2382,6 +2462,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67811322</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2485,6 +2570,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67811324</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2588,6 +2678,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67811325</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2691,6 +2786,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67811326</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2794,6 +2894,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67811327</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2907,6 +3012,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020, Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96353736</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3020,6 +3130,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020, Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96353758</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3133,6 +3248,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020, Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96353769</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3246,6 +3366,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020, Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96353788</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3359,6 +3484,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020, Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96354067</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3472,6 +3602,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020, Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96354179</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3585,6 +3720,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020, Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96354299</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3698,6 +3838,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020, Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96354311</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3811,6 +3956,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020, Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96354335</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3914,6 +4064,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67811189</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4025,6 +4180,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020, Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96354330</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4136,6 +4296,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020, Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96354327</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4255,6 +4420,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67811922</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4368,6 +4538,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67811919</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4481,6 +4656,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67811920</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4595,6 +4775,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020, Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96353724</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4697,6 +4882,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67811215</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4799,6 +4989,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67811218</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4901,8 +5096,54 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67811219</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>